--- a/Plan/Table/TestData/11.RequestData.xlsx
+++ b/Plan/Table/TestData/11.RequestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BF1120C-2C66-4D49-9ECF-88000DADF2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A25886D-FFA1-4A38-AB09-BB08C03665A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{4FC02ED5-D074-4858-A83B-DBCD3F517F60}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8AC4F938-594F-428B-A65C-B5D55740D88E}"/>
   </bookViews>
   <sheets>
     <sheet name="11.RequestData" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87BF0387-FF53-4704-AC7A-E20790C3654A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A62550-5EF4-4578-BA2B-61A76A2B9D66}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="K2">
         <v>101</v>
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="K3">
         <v>102</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="K4">
         <v>103</v>
